--- a/src/views/game/zlzq/cardList/zz_myCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/zz_myCard/z_level.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="11055" activeTab="1"/>
+    <workbookView windowWidth="14550" windowHeight="10830" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="帝国" sheetId="5" r:id="rId1"/>
-    <sheet name="隐秘" sheetId="6" r:id="rId2"/>
+    <sheet name="隐秘" sheetId="6" r:id="rId1"/>
+    <sheet name="帝国" sheetId="5" r:id="rId2"/>
     <sheet name="港口" sheetId="20" r:id="rId3"/>
     <sheet name="禅意" sheetId="7" r:id="rId4"/>
     <sheet name="阿斯塔拉" sheetId="2" r:id="rId5"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="503">
   <si>
     <t>名称</t>
   </si>
@@ -50,118 +50,256 @@
     <t>卡等</t>
   </si>
   <si>
+    <t>洞悉之眼</t>
+  </si>
+  <si>
+    <t>学仆-观测型1</t>
+  </si>
+  <si>
+    <t>学仆-观测型2</t>
+  </si>
+  <si>
+    <t>沉重否定</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术1</t>
+  </si>
+  <si>
+    <t>克隆术2</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型1</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型2</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型3</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>鬼童-7号</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>圣殿斥候1</t>
+  </si>
+  <si>
+    <t>圣殿斥候2</t>
+  </si>
+  <si>
+    <t>圣殿卫士</t>
+  </si>
+  <si>
+    <t>天使琼浆</t>
+  </si>
+  <si>
+    <t>炫目神光</t>
+  </si>
+  <si>
+    <t>圣殿弩手</t>
+  </si>
+  <si>
+    <t>田园守望者</t>
+  </si>
+  <si>
+    <t>增援战线</t>
+  </si>
+  <si>
+    <t>光明惩戒</t>
+  </si>
+  <si>
+    <t>夺取阵地</t>
+  </si>
+  <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>心灵黑洞1</t>
+  </si>
+  <si>
+    <t>心灵黑洞2</t>
+  </si>
+  <si>
+    <t>心灵黑洞3</t>
+  </si>
+  <si>
+    <t>狡诈学徒1</t>
+  </si>
+  <si>
+    <t>狡诈学徒2</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>红海猎魔人</t>
+  </si>
+  <si>
+    <t>海神赐福1</t>
+  </si>
+  <si>
+    <t>海神赐福2</t>
+  </si>
+  <si>
+    <t>海神赐福3</t>
+  </si>
+  <si>
+    <t>海燕·鲍莉</t>
+  </si>
+  <si>
+    <t>魔卡幻术师·梅基</t>
+  </si>
+  <si>
+    <t>赤影·艾希尔</t>
+  </si>
+  <si>
+    <t>港口卡等：</t>
+  </si>
+  <si>
+    <t>飓风术1</t>
+  </si>
+  <si>
+    <t>飓风术2</t>
+  </si>
+  <si>
+    <t>飓风术3</t>
+  </si>
+  <si>
+    <t>长耳庄巧姑1</t>
+  </si>
+  <si>
+    <t>长耳庄巧姑2</t>
+  </si>
+  <si>
+    <t>连击1</t>
+  </si>
+  <si>
+    <t>连击2</t>
+  </si>
+  <si>
+    <t>铁山靠1</t>
+  </si>
+  <si>
+    <t>铁山靠2</t>
+  </si>
+  <si>
+    <t>风铃道人</t>
+  </si>
+  <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>墨轩隐士</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>禅意卡等：</t>
+  </si>
+  <si>
     <t>圣殿斥候</t>
   </si>
   <si>
-    <t>圣殿卫士</t>
-  </si>
-  <si>
-    <t>天使琼浆</t>
-  </si>
-  <si>
-    <t>炫目神光</t>
-  </si>
-  <si>
-    <t>圣殿弩手</t>
-  </si>
-  <si>
-    <t>田园守望者</t>
-  </si>
-  <si>
-    <t>增援战线</t>
-  </si>
-  <si>
-    <t>光明惩戒</t>
-  </si>
-  <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>四芒军旗</t>
   </si>
   <si>
     <t>圣殿御卫</t>
   </si>
   <si>
-    <t>夺取阵地</t>
-  </si>
-  <si>
-    <t>惩戒天使</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>洞悉之眼</t>
-  </si>
-  <si>
-    <t>学仆-观测型1</t>
-  </si>
-  <si>
-    <t>学仆-观测型2</t>
-  </si>
-  <si>
-    <t>沉重否定</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>隐形术</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术1</t>
-  </si>
-  <si>
-    <t>克隆术2</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型1</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型2</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型3</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>鬼童-7号</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
+    <t>克隆术</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>花光春影·安娜贝尔</t>
+  </si>
+  <si>
+    <t>流星-7号</t>
+  </si>
+  <si>
+    <t>春花使者·卡洛琳</t>
+  </si>
+  <si>
+    <t>明日香·露娜</t>
+  </si>
+  <si>
+    <t>月之神·米拉</t>
+  </si>
+  <si>
+    <t>白袍·伊恩</t>
+  </si>
+  <si>
+    <t>总卡等：</t>
+  </si>
+  <si>
+    <t>武圣·云长</t>
   </si>
   <si>
     <t>心灵黑洞</t>
@@ -170,378 +308,285 @@
     <t>狡诈学徒</t>
   </si>
   <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>不法交易</t>
-  </si>
-  <si>
-    <t>红海猎魔人</t>
-  </si>
-  <si>
-    <t>海神赐福1</t>
-  </si>
-  <si>
-    <t>海神赐福2</t>
-  </si>
-  <si>
-    <t>海神赐福3</t>
+    <t>酗酒醉汉</t>
+  </si>
+  <si>
+    <t>占卜命运</t>
+  </si>
+  <si>
+    <t>走私狂徒</t>
+  </si>
+  <si>
+    <t>海神赐福</t>
+  </si>
+  <si>
+    <t>快乐使者</t>
   </si>
   <si>
     <t>黑金诈术师</t>
   </si>
   <si>
-    <t>海燕·鲍莉</t>
-  </si>
-  <si>
-    <t>魔卡幻术师·梅基</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
-  </si>
-  <si>
-    <t>港口卡等：</t>
+    <t>先发制人</t>
+  </si>
+  <si>
+    <t>学仆-猛禽型</t>
+  </si>
+  <si>
+    <t>黑水伏击</t>
+  </si>
+  <si>
+    <t>飓风术</t>
   </si>
   <si>
     <t>长耳庄巧姑</t>
   </si>
   <si>
-    <t>飓风术</t>
-  </si>
-  <si>
     <t>连击</t>
   </si>
   <si>
     <t>铁山靠</t>
   </si>
   <si>
-    <t>风铃道人</t>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>九天玄女·轩</t>
+  </si>
+  <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
+    <t>滑板少年·迪宁</t>
+  </si>
+  <si>
+    <t>种族</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>描述（20级数值）</t>
+  </si>
+  <si>
+    <t>帝国</t>
+  </si>
+  <si>
+    <t>蓝色</t>
+  </si>
+  <si>
+    <t>(22/18)：【洞察1】、【协战8】。</t>
+  </si>
+  <si>
+    <t>(25/30)：【洞察1】、【回命】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、英雄生命+66、抓一张牌、获得《真理石残片》。</t>
+  </si>
+  <si>
+    <t>大型弩车</t>
+  </si>
+  <si>
+    <t>(0/60)：【洞察1】、【协战25】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、召唤3个12/12民兵-lv17，75%概率再召唤一个。</t>
+  </si>
+  <si>
+    <t>塔楼弓手</t>
+  </si>
+  <si>
+    <t>(30/15)：【先攻】、洞察时:自身+6/+4、死亡:【洞察1】。</t>
+  </si>
+  <si>
+    <t>(20/28)：【洞察1】、洞察时:自身+5/+5，英雄获得生命（等同自身攻击）。</t>
+  </si>
+  <si>
+    <t>精英射手</t>
+  </si>
+  <si>
+    <t>(35/22)：【洞察1】、【先攻】、【协战9】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、横排所有敌军受到150点伤害、50%概率获得《真理碎片》。</t>
+  </si>
+  <si>
+    <t>紫色</t>
+  </si>
+  <si>
+    <t>(20/32)：【洞察1】、命中英雄:召唤16/8警卫-lv15。</t>
+  </si>
+  <si>
+    <t>边境高墙</t>
+  </si>
+  <si>
+    <t>(0/85)：【守军】、【磐龙】、【护甲8】、回合结束:【洞察1】，若场上有冰封，自身生命+15。</t>
+  </si>
+  <si>
+    <t>冲锋装备</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、目标友军+27/+27、并获得【护甲14】。</t>
+  </si>
+  <si>
+    <t>圣殿卫队长</t>
+  </si>
+  <si>
+    <t>(30/60)：【回命】、命中英雄:召唤16/21圣殿卫士-lv16。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、将横排敌军移回玩家手上、友军横排召唤21/9警卫-lv18。</t>
+  </si>
+  <si>
+    <t>召集护卫</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、在目标位置和随机位置，召唤3/60圣堂门卫-lv20、护甲友军攻击+12，获得【磐龙】1回合。</t>
+  </si>
+  <si>
+    <t>皇家射手</t>
+  </si>
+  <si>
+    <t>(40/20)：【先攻】、【洞察1】、回合开始:召唤25/12塔楼弓手-lv18（次数上限：3）。</t>
+  </si>
+  <si>
+    <t>(40/80)：【回命】、【洞察3】、登场:消灭对面横排首位新进场敌军。</t>
+  </si>
+  <si>
+    <t>禁卫指挥官</t>
+  </si>
+  <si>
+    <t>(30/54)：【洞察1】、【护甲8】、洞察时：全体友军+6/+6。</t>
+  </si>
+  <si>
+    <t>橙色</t>
+  </si>
+  <si>
+    <t>(20/32)：【洞察2】、攻击前:所有友军+6/+6，魔防+3。（皮肤：命中时：另一友军+1/+1。）</t>
+  </si>
+  <si>
+    <t>百花长枪·卡洛琳</t>
+  </si>
+  <si>
+    <t>(36/36)：【回命】、【神佑】、【护甲15】。（皮肤：命中时：【洞察1】，50几率英雄生命额外+10。）</t>
+  </si>
+  <si>
+    <t>(0/20)：【魔防20】、同横排其他单位不会攻击（无视神佑和魔免）、回合结束:【洞察1】、另一友军+7/+15。（皮肤：登场：其他全体友军，攻击+3，本回合护甲+X（X等同露娜等级）。）</t>
+  </si>
+  <si>
+    <t>(20/70)：登场:英雄生命+70、英雄获得生命:回复效果加倍，自身+3/+13，其他友军+4/+4。（皮肤：【洞察1】、洞察时：自身魔防+2，其他友军攻击+1。）</t>
+  </si>
+  <si>
+    <t>隐秘</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、英雄生命+30。</t>
+  </si>
+  <si>
+    <t>方尖魔碑</t>
+  </si>
+  <si>
+    <t>(0/40)：【守军】、敌方法力上限-1、回合结束:70%几率【洞察1】。</t>
+  </si>
+  <si>
+    <t>(22/32)：洞察时：自身+4/+4、死亡：【洞察1】，英雄恢复生命（等同攻击力）。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、横排敌军攻击-33。</t>
+  </si>
+  <si>
+    <t>学仆-渗透型</t>
+  </si>
+  <si>
+    <t>(35/35)：【洞察1】、【穿透】、【护甲8】。</t>
+  </si>
+  <si>
+    <t>请示隐秘者</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、抽2张牌、随机友军生命+66、充能:多抽一张牌。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、目标单位+23/+23，获得【隐形】。</t>
+  </si>
+  <si>
+    <t>(21/27)：【洞察1】、登场:沉默随机敌军、命中时:65%几率【洞察1】、回合结束:35%几率沉默随机敌军。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、复制目标单位到手上，英雄生命+40。</t>
+  </si>
+  <si>
+    <t>神秘学教授</t>
+  </si>
+  <si>
+    <t>(13/33)：每当一个敌军死亡:获得【洞悉之眼-lv20】（每次对战仅可触发3次）。</t>
+  </si>
+  <si>
+    <t>(27/15)：【先攻】、命中时：【洞察1】、洞察时：全体先攻友军攻击+9。</t>
+  </si>
+  <si>
+    <t>(16/30)：【洞察1】、洞察时：自身+3/+8，射击英雄。</t>
+  </si>
+  <si>
+    <t>白首魔根</t>
+  </si>
+  <si>
+    <t>(17/67)：【洞察1】、【魔免】、回合结束:自身攻击加倍。</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>(0/54)：【洞察1】、【魔防6】、法力上限+2、回合开始:随机敌军-x/-x(x为你的法力)。</t>
+  </si>
+  <si>
+    <t>学仆-塑钢型</t>
+  </si>
+  <si>
+    <t>(38/38)：【磐龙】、【护甲15】、洞察时：自身+3/+6，护甲+3。</t>
+  </si>
+  <si>
+    <t>(20/35)：【洞察1】、【魔防20】、洞察时：抽一张牌。</t>
+  </si>
+  <si>
+    <t>(50/100)：【洞察1】、【磐龙】、【穿透】、【护甲15】、【魔防15】、洞察时：获得《渗透型》lv20、护甲友军死亡：自身+8/+24。</t>
+  </si>
+  <si>
+    <t>(29/25)：法力上限+3，你的法术卡使用后，移回手上、死亡:自身回手，75%概率获得沉默术-lv11。（皮肤：【洞察1】、洞察时：英雄生命+3。）</t>
+  </si>
+  <si>
+    <t>(25/25)：【魔防15】、【先攻】、回合开始：全体先攻友军+4/+4、获得【连击】1回合。（皮肤：登场：【洞察1】、全体先攻友军获得【隐形】和【神佑】1回合。）</t>
+  </si>
+  <si>
+    <t>禅意</t>
+  </si>
+  <si>
+    <t>(14/15)：【洞察1】、【传承10】、法力上限+1。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、目标敌军吹回手上、英雄生命+36。</t>
+  </si>
+  <si>
+    <t>锁妖塔守卫</t>
+  </si>
+  <si>
+    <t>(30/30)：【洞察1】、【法力封锁1】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、目标友军加攻，等同其一半生命值、另一友军生命+24、75%几率抽一张牌。</t>
+  </si>
+  <si>
+    <t>明月曲</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、7个友军+7/+7、抽一张牌。</t>
+  </si>
+  <si>
+    <t>(29/29)：【洞察1】、登场:吹回随机敌军。</t>
   </si>
   <si>
     <t>蟠桃隐士</t>
   </si>
   <si>
-    <t>驱魔道人</t>
-  </si>
-  <si>
-    <t>墨轩隐士</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
-  </si>
-  <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
-  </si>
-  <si>
-    <t>禅意卡等：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>四芒军旗</t>
-  </si>
-  <si>
-    <t>克隆术</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
-    <t>花光春影·安娜贝尔</t>
-  </si>
-  <si>
-    <t>流星-7号</t>
-  </si>
-  <si>
-    <t>春花使者·卡洛琳</t>
-  </si>
-  <si>
-    <t>明日香·露娜</t>
-  </si>
-  <si>
-    <t>月之神·米拉</t>
-  </si>
-  <si>
-    <t>白袍·伊恩</t>
-  </si>
-  <si>
-    <t>总卡等：</t>
-  </si>
-  <si>
-    <t>武圣·云长</t>
-  </si>
-  <si>
-    <t>酗酒醉汉</t>
-  </si>
-  <si>
-    <t>占卜命运</t>
-  </si>
-  <si>
-    <t>走私狂徒</t>
-  </si>
-  <si>
-    <t>海神赐福</t>
-  </si>
-  <si>
-    <t>快乐使者</t>
-  </si>
-  <si>
-    <t>先发制人</t>
-  </si>
-  <si>
-    <t>学仆-猛禽型</t>
-  </si>
-  <si>
-    <t>黑水伏击</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>九天玄女·轩</t>
-  </si>
-  <si>
-    <t>上宝沁金耙</t>
-  </si>
-  <si>
-    <t>滑板少年·迪宁</t>
-  </si>
-  <si>
-    <t>种族</t>
-  </si>
-  <si>
-    <t>品质</t>
-  </si>
-  <si>
-    <t>描述（20级数值）</t>
-  </si>
-  <si>
-    <t>帝国</t>
-  </si>
-  <si>
-    <t>蓝色</t>
-  </si>
-  <si>
-    <t>(22/18)：【洞察1】、【协战8】。</t>
-  </si>
-  <si>
-    <t>(25/30)：【洞察1】、【回命】。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、英雄生命+66、抓一张牌、获得《真理石残片》。</t>
-  </si>
-  <si>
-    <t>大型弩车</t>
-  </si>
-  <si>
-    <t>(0/60)：【洞察1】、【协战25】。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、召唤3个12/12民兵-lv17，75%概率再召唤一个。</t>
-  </si>
-  <si>
-    <t>塔楼弓手</t>
-  </si>
-  <si>
-    <t>(30/15)：【先攻】、洞察时:自身+6/+4、死亡:【洞察1】。</t>
-  </si>
-  <si>
-    <t>(20/28)：【洞察1】、洞察时:自身+5/+5，英雄获得生命（等同自身攻击）。</t>
-  </si>
-  <si>
-    <t>精英射手</t>
-  </si>
-  <si>
-    <t>(35/22)：【洞察1】、【先攻】、【协战9】。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、横排所有敌军受到150点伤害、50%概率获得《真理碎片》。</t>
-  </si>
-  <si>
-    <t>紫色</t>
-  </si>
-  <si>
-    <t>(20/32)：【洞察1】、命中英雄:召唤16/8警卫-lv15。</t>
-  </si>
-  <si>
-    <t>边境高墙</t>
-  </si>
-  <si>
-    <t>(0/85)：【守军】、【磐龙】、【护甲8】、回合结束:【洞察1】，若场上有冰封，自身生命+15。</t>
-  </si>
-  <si>
-    <t>冲锋装备</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、目标友军+27/+27、并获得【护甲14】。</t>
-  </si>
-  <si>
-    <t>圣殿卫队长</t>
-  </si>
-  <si>
-    <t>(30/60)：【回命】、命中英雄:召唤16/21圣殿卫士-lv16。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、将横排敌军移回玩家手上、友军横排召唤21/9警卫-lv18。</t>
-  </si>
-  <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、在目标位置和随机位置，召唤3/60圣堂门卫-lv20、护甲友军攻击+12，获得【磐龙】1回合。</t>
-  </si>
-  <si>
-    <t>皇家射手</t>
-  </si>
-  <si>
-    <t>(40/20)：【先攻】、【洞察1】、回合开始:召唤25/12塔楼弓手-lv18（次数上限：3）。</t>
-  </si>
-  <si>
-    <t>(40/80)：【回命】、【洞察3】、登场:消灭对面横排首位新进场敌军。</t>
-  </si>
-  <si>
-    <t>禁卫指挥官</t>
-  </si>
-  <si>
-    <t>(30/54)：【洞察1】、【护甲8】、洞察时：全体友军+6/+6。</t>
-  </si>
-  <si>
-    <t>橙色</t>
-  </si>
-  <si>
-    <t>(20/32)：【洞察2】、攻击前:所有友军+6/+6，魔防+3。（皮肤：命中时：另一友军+1/+1。）</t>
-  </si>
-  <si>
-    <t>百花长枪·卡洛琳</t>
-  </si>
-  <si>
-    <t>(36/36)：【回命】、【神佑】、【护甲15】。（皮肤：命中时：【洞察1】，50几率英雄生命额外+10。）</t>
-  </si>
-  <si>
-    <t>(0/20)：【魔防20】、同横排其他单位不会攻击（无视神佑和魔免）、回合结束:【洞察1】、另一友军+7/+15。（皮肤：登场：其他全体友军，攻击+3，本回合护甲+X（X等同露娜等级）。）</t>
-  </si>
-  <si>
-    <t>(20/70)：登场:英雄生命+70、英雄获得生命:回复效果加倍，自身+3/+13，其他友军+4/+4。（皮肤：【洞察1】、洞察时：自身魔防+2，其他友军攻击+1。）</t>
-  </si>
-  <si>
-    <t>隐秘</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、英雄生命+30。</t>
-  </si>
-  <si>
-    <t>方尖魔碑</t>
-  </si>
-  <si>
-    <t>(0/40)：【守军】、敌方法力上限-1、回合结束:70%几率【洞察1】。</t>
-  </si>
-  <si>
-    <t>(22/32)：洞察时：自身+4/+4、死亡：【洞察1】，英雄恢复生命（等同攻击力）。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、横排敌军攻击-33。</t>
-  </si>
-  <si>
-    <t>学仆-渗透型</t>
-  </si>
-  <si>
-    <t>(35/35)：【洞察1】、【穿透】、【护甲8】。</t>
-  </si>
-  <si>
-    <t>请示隐秘者</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、抽2张牌、随机友军生命+66、充能:多抽一张牌。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、目标单位+23/+23，获得【隐形】。</t>
-  </si>
-  <si>
-    <t>(21/27)：【洞察1】、登场:沉默随机敌军、命中时:65%几率【洞察1】、回合结束:35%几率沉默随机敌军。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、复制目标单位到手上，英雄生命+40。</t>
-  </si>
-  <si>
-    <t>神秘学教授</t>
-  </si>
-  <si>
-    <t>(13/33)：每当一个敌军死亡:获得【洞悉之眼-lv20】（每次对战仅可触发3次）。</t>
-  </si>
-  <si>
-    <t>(27/15)：【先攻】、命中时：【洞察1】、洞察时：全体先攻友军攻击+9。</t>
-  </si>
-  <si>
-    <t>(16/30)：【洞察1】、洞察时：自身+3/+8，射击英雄。</t>
-  </si>
-  <si>
-    <t>白首魔根</t>
-  </si>
-  <si>
-    <t>(17/67)：【洞察1】、【魔免】、回合结束:自身攻击加倍。</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>(0/54)：【洞察1】、【魔防6】、法力上限+2、回合开始:随机敌军-x/-x(x为你的法力)。</t>
-  </si>
-  <si>
-    <t>学仆-塑钢型</t>
-  </si>
-  <si>
-    <t>(38/38)：【磐龙】、【护甲15】、洞察时：自身+3/+6，护甲+3。</t>
-  </si>
-  <si>
-    <t>(20/35)：【洞察1】、【魔防20】、洞察时：抽一张牌。</t>
-  </si>
-  <si>
-    <t>(50/100)：【洞察1】、【磐龙】、【穿透】、【护甲15】、【魔防15】、洞察时：获得《渗透型》lv20、护甲友军死亡：自身+8/+24。</t>
-  </si>
-  <si>
-    <t>(29/25)：法力上限+3，你的法术卡使用后，移回手上、死亡:自身回手，75%概率获得沉默术-lv11。（皮肤：【洞察1】、洞察时：英雄生命+3。）</t>
-  </si>
-  <si>
-    <t>(25/25)：【魔防15】、【先攻】、回合开始：全体先攻友军+4/+4、获得【连击】1回合。（皮肤：登场：【洞察1】、全体先攻友军获得【隐形】和【神佑】1回合。）</t>
-  </si>
-  <si>
-    <t>禅意</t>
-  </si>
-  <si>
-    <t>(14/15)：【洞察1】、【传承10】、法力上限+1。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、目标敌军吹回手上、英雄生命+36。</t>
-  </si>
-  <si>
-    <t>锁妖塔守卫</t>
-  </si>
-  <si>
-    <t>(30/30)：【洞察1】、【法力封锁1】。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、目标友军加攻，等同其一半生命值、另一友军生命+24、75%几率抽一张牌。</t>
-  </si>
-  <si>
-    <t>明月曲</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、7个友军+7/+7、抽一张牌。</t>
-  </si>
-  <si>
-    <t>(29/29)：【洞察1】、登场:吹回随机敌军。</t>
-  </si>
-  <si>
     <t>(0/60)：【洞察1】、回合结束:获得手牌:仙桃-lv20。</t>
   </si>
   <si>
@@ -1427,15 +1472,9 @@
     <t>所需时间</t>
   </si>
   <si>
-    <t>圣殿斥候1</t>
-  </si>
-  <si>
     <t>/</t>
   </si>
   <si>
-    <t>圣殿斥候2</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -1470,9 +1509,6 @@
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
   </si>
   <si>
     <t>帝国军魂·莱哈特</t>
@@ -2485,15 +2521,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="17.125" customWidth="1"/>
+    <col min="2" max="2" width="10.2583333333333" customWidth="1"/>
+    <col min="3" max="3" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2504,18 +2540,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2526,7 +2562,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -2537,7 +2573,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -2548,7 +2584,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -2559,63 +2595,62 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>22</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
@@ -2623,18 +2658,18 @@
         <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2642,65 +2677,65 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>7</v>
       </c>
       <c r="C20" s="2">
-        <f>AVERAGE(C15:C17)</f>
-        <v>17</v>
-      </c>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="3">
-        <v>4</v>
-      </c>
-      <c r="C24" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
+      <c r="A23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="3">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3">
-        <v>15</v>
+      <c r="C23" s="2">
+        <f>AVERAGE(C12:C20)</f>
+        <v>20.3333333333333</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2708,16 +2743,22 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3">
+        <v>20</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -2725,27 +2766,32 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="3" t="s">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3">
+        <f>AVERAGE(C26:C27)</f>
         <v>21</v>
       </c>
-      <c r="C29" s="3">
-        <f>AVERAGE(C23:C26)</f>
-        <v>19.25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B33" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C9,C15:C17,C23:C26)</f>
-        <v>20.2666666666667</v>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C6,C12:C20,C26:C27)</f>
+        <v>20.5625</v>
       </c>
     </row>
   </sheetData>
@@ -2769,19 +2815,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2789,2365 +2835,2365 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D10">
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D11">
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D12">
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="D20">
         <v>6</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D21">
         <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D23">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D24">
         <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D29">
         <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D30">
         <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D34">
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D42">
         <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D43">
         <v>7</v>
       </c>
       <c r="E43" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D44">
         <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D45">
         <v>6</v>
       </c>
       <c r="E45" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D48">
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D49">
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B50" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="E50" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D51">
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B52" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D53">
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B54" t="s">
-        <v>60</v>
+        <v>181</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D55">
         <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D56">
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D57">
         <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B58" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D58">
         <v>5</v>
       </c>
       <c r="E58" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B59" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D59">
         <v>4</v>
       </c>
       <c r="E59" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B62" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B63" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D63">
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B64" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D64">
         <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B65" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D65">
         <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B66" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D66">
         <v>2</v>
       </c>
       <c r="E66" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D67">
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D68">
         <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B69" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D69">
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B70" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D70">
         <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B71" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D71">
         <v>2</v>
       </c>
       <c r="E71" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B72" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D72">
         <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B73" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D73">
         <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B74" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D74">
         <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B75" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D75">
         <v>4</v>
       </c>
       <c r="E75" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B78" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D78">
         <v>2</v>
       </c>
       <c r="E78" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B79" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D79">
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B80" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D80">
         <v>3</v>
       </c>
       <c r="E80" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B81" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D81">
         <v>4</v>
       </c>
       <c r="E81" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B82" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D82">
         <v>3</v>
       </c>
       <c r="E82" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B83" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D83">
         <v>5</v>
       </c>
       <c r="E83" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B86" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B87" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D87">
         <v>2</v>
       </c>
       <c r="E87" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B88" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D88">
         <v>2</v>
       </c>
       <c r="E88" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B89" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D89">
         <v>2</v>
       </c>
       <c r="E89" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B90" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D90">
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B91" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D91">
         <v>3</v>
       </c>
       <c r="E91" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B92" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D92">
         <v>3</v>
       </c>
       <c r="E92" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B93" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D93">
         <v>3</v>
       </c>
       <c r="E93" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B94" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D94">
         <v>4</v>
       </c>
       <c r="E94" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B95" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D95">
         <v>4</v>
       </c>
       <c r="E95" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B96" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D96">
         <v>4</v>
       </c>
       <c r="E96" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B97" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D97">
         <v>5</v>
       </c>
       <c r="E97" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B98" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D98">
         <v>5</v>
       </c>
       <c r="E98" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B99" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D99">
         <v>2</v>
       </c>
       <c r="E99" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B100" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D100">
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B101" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D101">
         <v>3</v>
       </c>
       <c r="E101" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B102" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D102">
         <v>4</v>
       </c>
       <c r="E102" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B105" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D105">
         <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B106" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D106">
         <v>2</v>
       </c>
       <c r="E106" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B107" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D107">
         <v>3</v>
       </c>
       <c r="E107" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B108" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D108">
         <v>3</v>
       </c>
       <c r="E108" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B109" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D109">
         <v>2</v>
       </c>
       <c r="E109" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B110" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D110">
         <v>3</v>
       </c>
       <c r="E110" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B111" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D111">
         <v>4</v>
       </c>
       <c r="E111" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B112" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D112">
         <v>6</v>
       </c>
       <c r="E112" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B117" t="s">
         <v>0</v>
       </c>
       <c r="C117" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D117" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="E117" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B118" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D118" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E118" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B119" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D119" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E119" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B120" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D120" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E120" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B121" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D121" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E121" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B122" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D122" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E122" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B123" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D123" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E123" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B124" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D124" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E124" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B125" t="s">
+        <v>294</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D125" t="s">
         <v>279</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D125" t="s">
-        <v>264</v>
-      </c>
       <c r="E125" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B126" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D126" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E126" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B127" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D127" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E127" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B128" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D128" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E128" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B129" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D129" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E129" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B130" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D130" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E130" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B131" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D131" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E131" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B132" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D132" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E132" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B133" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D133" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E133" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B134" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D134" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E134" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B135" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D135" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E135" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B136" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D136" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E136" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B137" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D137" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E137" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B138" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D138" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E138" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B139" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D139" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E139" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B140" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D140" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E140" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B141" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D141" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E141" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B142" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D142" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E142" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B143" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D143" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E143" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B144" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D144" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E144" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B145" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D145" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E145" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B146" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D146" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E146" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B147" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D147" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E147" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B148" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D148" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E148" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B149" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D149" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="E149" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B150" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D150" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E150" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B151" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D151" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E151" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B152" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D152" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E152" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B153" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D153" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E153" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B154" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D154" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E154" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B155" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E155" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B156" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D156" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E156" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B157" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D157" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="E157" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -5171,1124 +5217,1124 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B9" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B15" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B17" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B19" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="D20">
         <v>6</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D21">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B23" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D23">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B24" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D24">
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B26" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D26">
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D27">
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B28" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D28">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B33" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B34" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D34">
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B36" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D36">
         <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D37">
         <v>7</v>
       </c>
       <c r="E37" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B38" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D38">
         <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B39" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D39">
         <v>2</v>
       </c>
       <c r="E39" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B40" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D40">
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B43" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B44" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D44">
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B45" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D45">
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B46" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D46">
         <v>4</v>
       </c>
       <c r="E46" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B47" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D47">
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B48" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D48">
         <v>6</v>
       </c>
       <c r="E48" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D49">
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B50" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D50">
         <v>6</v>
       </c>
       <c r="E50" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="B53" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D53">
         <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D54">
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B57" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D57">
         <v>2</v>
       </c>
       <c r="E57" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B58" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D58">
         <v>4</v>
       </c>
       <c r="E58" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B59" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B60" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:5">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B61" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D61">
         <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:5">
       <c r="A62" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B62" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D62">
         <v>5</v>
       </c>
       <c r="E62" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:5">
       <c r="A63" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B63" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D63">
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:5">
       <c r="A64" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B64" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D64">
         <v>4</v>
       </c>
       <c r="E64" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:5">
       <c r="A65" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B65" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D65">
         <v>5</v>
       </c>
       <c r="E65" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B68" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D68">
         <v>2</v>
       </c>
       <c r="E68" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B69" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D69">
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B72" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D72">
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B73" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D73">
         <v>4</v>
       </c>
       <c r="E73" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B74" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D74">
         <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B75" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D75">
         <v>5</v>
       </c>
       <c r="E75" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B76" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D76">
         <v>5</v>
       </c>
       <c r="E76" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B77" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D77">
         <v>5</v>
       </c>
       <c r="E77" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B78" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D78">
         <v>6</v>
       </c>
       <c r="E78" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -6317,33 +6363,33 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C1" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="D1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E1" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="F1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="G1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>462</v>
+        <v>24</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C2" s="1">
         <v>18</v>
@@ -6356,15 +6402,15 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>464</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -6377,18 +6423,18 @@
         <v>2684</v>
       </c>
       <c r="F3" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="G3" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C4" s="1">
         <v>17</v>
@@ -6403,10 +6449,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C5" s="1">
         <v>18</v>
@@ -6421,10 +6467,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C6" s="1">
         <v>18</v>
@@ -6439,10 +6485,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
@@ -6455,15 +6501,15 @@
         <v>2640</v>
       </c>
       <c r="F7" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C8" s="1">
         <v>16</v>
@@ -6478,10 +6524,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C9" s="1">
         <v>16</v>
@@ -6496,10 +6542,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C10" s="1">
         <v>16</v>
@@ -6514,10 +6560,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C11" s="1">
         <v>6</v>
@@ -6532,10 +6578,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2">
         <v>18</v>
@@ -6548,15 +6594,15 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
@@ -6571,10 +6617,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C14" s="2">
         <v>17</v>
@@ -6589,10 +6635,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C15" s="2">
         <v>15</v>
@@ -6607,10 +6653,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C16" s="2">
         <v>14</v>
@@ -6623,15 +6669,15 @@
         <v>955</v>
       </c>
       <c r="F16" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C17" s="2">
         <v>16</v>
@@ -6646,10 +6692,10 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2">
         <v>15</v>
@@ -6664,10 +6710,10 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C19" s="2">
         <v>4</v>
@@ -6682,10 +6728,10 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C20" s="2">
         <v>4</v>
@@ -6700,10 +6746,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -6718,10 +6764,10 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C22" s="2">
         <v>7</v>
@@ -6736,10 +6782,10 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C23" s="2">
         <v>5</v>
@@ -6754,10 +6800,10 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C24" s="3">
         <v>13</v>
@@ -6770,15 +6816,15 @@
         <v>552</v>
       </c>
       <c r="F24" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C25" s="3">
         <v>16</v>
@@ -6791,15 +6837,15 @@
         <v>382</v>
       </c>
       <c r="F25" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C26" s="3">
         <v>13</v>
@@ -6812,15 +6858,15 @@
         <v>726</v>
       </c>
       <c r="F26" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C27" s="3">
         <v>15</v>
@@ -6833,15 +6879,15 @@
         <v>470</v>
       </c>
       <c r="F27" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
-        <v>477</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C28" s="3">
         <v>14</v>
@@ -6854,15 +6900,15 @@
         <v>629</v>
       </c>
       <c r="F28" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C29" s="3">
         <v>2</v>
@@ -6877,10 +6923,10 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -6893,15 +6939,15 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C35" s="1">
         <v>16</v>
@@ -6916,10 +6962,10 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C36" s="1">
         <v>17</v>
@@ -6932,15 +6978,15 @@
         <v>149</v>
       </c>
       <c r="F36" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C37" s="1">
         <v>13</v>
@@ -6953,15 +6999,15 @@
         <v>1648</v>
       </c>
       <c r="F37" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C38" s="1">
         <v>13</v>
@@ -6974,15 +7020,15 @@
         <v>1856</v>
       </c>
       <c r="F38" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C39" s="1">
         <v>18</v>
@@ -6995,15 +7041,15 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C40" s="1">
         <v>6</v>
@@ -7018,10 +7064,10 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C41" s="1">
         <v>6</v>
@@ -7036,10 +7082,10 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C42" s="2">
         <v>14</v>
@@ -7052,15 +7098,15 @@
         <v>1105</v>
       </c>
       <c r="F42" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C43" s="2">
         <v>16</v>
@@ -7073,15 +7119,15 @@
         <v>438</v>
       </c>
       <c r="F43" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C44" s="2">
         <v>14</v>
@@ -7094,15 +7140,15 @@
         <v>911</v>
       </c>
       <c r="F44" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C45" s="2">
         <v>17</v>
@@ -7115,18 +7161,18 @@
         <v>279</v>
       </c>
       <c r="F45" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="G45" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C46" s="2">
         <v>17</v>
@@ -7139,15 +7185,15 @@
         <v>320</v>
       </c>
       <c r="F46" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -7162,10 +7208,10 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C48" s="2">
         <v>15</v>
@@ -7180,10 +7226,10 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C49" s="2">
         <v>13</v>
@@ -7198,10 +7244,10 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C50" s="2">
         <v>17</v>
@@ -7214,15 +7260,15 @@
         <v>320</v>
       </c>
       <c r="F50" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C51" s="2">
         <v>10</v>
@@ -7235,15 +7281,15 @@
         <v>953</v>
       </c>
       <c r="F51" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C52" s="3">
         <v>3</v>
@@ -7258,10 +7304,10 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C53" s="3">
         <v>2</v>
@@ -7276,10 +7322,10 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C54" s="3">
         <v>12</v>
@@ -7292,15 +7338,15 @@
         <v>477</v>
       </c>
       <c r="F54" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C55" s="3">
         <v>6</v>
@@ -7315,10 +7361,10 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C56" s="3">
         <v>3</v>
@@ -7351,16 +7397,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="B1" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="C1" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="D1" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7652,15 +7698,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="17.125" customWidth="1"/>
-    <col min="2" max="2" width="10.2583333333333" customWidth="1"/>
-    <col min="3" max="3" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7671,29 +7717,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -7704,7 +7750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
@@ -7712,95 +7758,96 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3">
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3</v>
       </c>
       <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="B10" s="1">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1">
+        <f>AVERAGE(C2:C10)</f>
+        <v>22</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7808,65 +7855,65 @@
         <v>34</v>
       </c>
       <c r="B17" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="2">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2">
-        <v>22</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="2">
-        <v>5</v>
-      </c>
-      <c r="C19" s="2">
-        <v>12</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C16:C17)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="3">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="2">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2">
+      <c r="B25" s="3">
+        <v>6</v>
+      </c>
+      <c r="C25" s="3">
         <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="2">
-        <f>AVERAGE(C12:C20)</f>
-        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7874,22 +7921,16 @@
         <v>38</v>
       </c>
       <c r="B26" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C26" s="3">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3">
-        <v>5</v>
-      </c>
-      <c r="C27" s="3">
-        <v>16</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -7897,32 +7938,27 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C26:C27)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
+      <c r="A29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C23:C26)</f>
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C6,C12:C20,C26:C27)</f>
-        <v>19.0625</v>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C10,C16:C17,C23:C26)</f>
+        <v>20.1333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -7966,29 +8002,29 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -7999,21 +8035,21 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1">
         <v>22</v>
@@ -8021,19 +8057,25 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="1">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>18</v>
+      </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1"/>
@@ -8041,42 +8083,36 @@
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>20</v>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1">
+        <f>AVERAGE(C2:C9)</f>
+        <v>17.75</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -8087,7 +8123,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
@@ -8098,13 +8134,13 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -8119,19 +8155,19 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C21" s="2">
-        <f>AVERAGE(C14:C18)</f>
-        <v>14.2</v>
+        <f>AVERAGE(C15:C18)</f>
+        <v>14.5</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
@@ -8142,18 +8178,18 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -8174,14 +8210,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C24:C26)</f>
-        <v>12</v>
+        <v>12.6666666666667</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8189,11 +8225,11 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C8,C14:C18,C24:C26)</f>
-        <v>15.5333333333333</v>
+        <f>AVERAGE(C2:C9,C15:C18,C24:C26)</f>
+        <v>15.8666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -8226,43 +8262,43 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
         <v>12</v>
@@ -8270,10 +8306,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1">
         <v>12</v>
@@ -8281,21 +8317,21 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1">
         <v>12</v>
@@ -8303,73 +8339,73 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B9" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="1">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="1">
-        <f>AVERAGE(C2:C9)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>12</v>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1">
+        <f>AVERAGE(C2:C11)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -8380,19 +8416,25 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B19" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="2">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2"/>
@@ -8400,37 +8442,31 @@
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C15:C19)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="3">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3">
-        <v>15</v>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="2">
+        <f>AVERAGE(C17:C20)</f>
+        <v>14.25</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -8445,14 +8481,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C25:C26)</f>
-        <v>13.5</v>
+        <f>AVERAGE(C26:C26)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -8460,11 +8496,11 @@
         <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C9,C15:C19,C25:C26)</f>
-        <v>12.2</v>
+        <f>AVERAGE(C2:C11,C17:C20,C26:C26)</f>
+        <v>13.4666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -8497,7 +8533,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -8508,7 +8544,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -8519,7 +8555,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -8530,7 +8566,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -8541,7 +8577,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -8552,7 +8588,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -8563,7 +8599,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -8574,7 +8610,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -8585,7 +8621,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -8596,7 +8632,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -8607,7 +8643,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
@@ -8618,7 +8654,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>5</v>
@@ -8639,10 +8675,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C16" s="1">
         <f>AVERAGE(C2:C13)</f>
@@ -8651,7 +8687,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -8662,7 +8698,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -8673,7 +8709,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -8684,7 +8720,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
@@ -8695,7 +8731,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B23" s="2">
         <v>2</v>
@@ -8706,7 +8742,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2">
         <v>3</v>
@@ -8717,7 +8753,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B25" s="2">
         <v>3</v>
@@ -8728,7 +8764,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
@@ -8739,7 +8775,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2">
         <v>4</v>
@@ -8750,7 +8786,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B28" s="2">
         <v>5</v>
@@ -8761,7 +8797,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2">
         <v>6</v>
@@ -8772,7 +8808,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B30" s="2">
         <v>7</v>
@@ -8793,10 +8829,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C33" s="2">
         <f>AVERAGE(C19:C30)</f>
@@ -8805,7 +8841,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B36" s="3">
         <v>3</v>
@@ -8816,7 +8852,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B37" s="3">
         <v>4</v>
@@ -8827,7 +8863,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B38" s="3">
         <v>4</v>
@@ -8838,7 +8874,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B39" s="3">
         <v>4</v>
@@ -8849,7 +8885,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B40" s="3">
         <v>5</v>
@@ -8860,7 +8896,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B41" s="3">
         <v>6</v>
@@ -8881,10 +8917,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C44" s="3">
         <f>AVERAGE(C36:C41)</f>
@@ -8896,7 +8932,7 @@
         <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C47">
         <f>AVERAGE(C2:C13,C19:C30,C36:C41)</f>
@@ -8934,7 +8970,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -8945,7 +8981,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -8956,7 +8992,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -8967,7 +9003,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -8978,7 +9014,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -8989,7 +9025,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -9000,7 +9036,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -9011,7 +9047,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -9022,7 +9058,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -9033,7 +9069,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -9044,7 +9080,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
@@ -9055,7 +9091,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>5</v>
@@ -9076,10 +9112,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C16" s="1">
         <f>AVERAGE(C2:C13)</f>
@@ -9088,7 +9124,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -9099,7 +9135,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -9110,7 +9146,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -9121,7 +9157,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
@@ -9132,7 +9168,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B23" s="2">
         <v>2</v>
@@ -9143,7 +9179,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2">
         <v>3</v>
@@ -9154,7 +9190,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B25" s="2">
         <v>3</v>
@@ -9165,7 +9201,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
@@ -9176,7 +9212,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2">
         <v>4</v>
@@ -9187,7 +9223,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2">
         <v>6</v>
@@ -9199,7 +9235,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B29" s="2">
         <v>7</v>
@@ -9221,10 +9257,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C32" s="2">
         <f>AVERAGE(C19:C29)</f>
@@ -9233,7 +9269,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B35" s="3">
         <v>3</v>
@@ -9244,7 +9280,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B36" s="3">
         <v>4</v>
@@ -9255,7 +9291,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B37" s="3">
         <v>4</v>
@@ -9266,7 +9302,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B38" s="3">
         <v>4</v>
@@ -9277,7 +9313,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B39" s="3">
         <v>5</v>
@@ -9288,7 +9324,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B40" s="3">
         <v>6</v>
@@ -9299,7 +9335,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B41" s="3">
         <v>8</v>
@@ -9320,10 +9356,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C44" s="3">
         <f>AVERAGE(C35:C41)</f>
@@ -9335,7 +9371,7 @@
         <v>22</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C47" s="4">
         <f>AVERAGE(C2:C13,C19:C29,C35:C41)</f>
@@ -9373,7 +9409,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -9384,7 +9420,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1">
         <v>0</v>
@@ -9395,7 +9431,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -9406,7 +9442,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -9417,7 +9453,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -9428,7 +9464,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -9439,7 +9475,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -9450,7 +9486,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -9461,7 +9497,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
@@ -9472,7 +9508,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -9483,7 +9519,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
@@ -9494,7 +9530,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B13" s="1">
         <v>3</v>
@@ -9505,7 +9541,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1">
         <v>3</v>
@@ -9516,7 +9552,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B15" s="1">
         <v>3</v>
@@ -9537,10 +9573,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C18" s="1">
         <f>AVERAGE(C2:C15)</f>
@@ -9549,7 +9585,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -9560,7 +9596,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
@@ -9571,7 +9607,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B23" s="2">
         <v>2</v>
@@ -9582,7 +9618,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B24" s="2">
         <v>2</v>
@@ -9593,7 +9629,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B25" s="2">
         <v>2</v>
@@ -9604,7 +9640,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B26" s="2">
         <v>2</v>
@@ -9615,7 +9651,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B27" s="2">
         <v>2</v>
@@ -9626,7 +9662,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B28" s="2">
         <v>3</v>
@@ -9637,7 +9673,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B29" s="2">
         <v>3</v>
@@ -9649,7 +9685,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B30" s="2">
         <v>3</v>
@@ -9661,7 +9697,7 @@
     </row>
     <row r="31" ht="14" customHeight="1" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="B31" s="2">
         <v>4</v>
@@ -9673,7 +9709,7 @@
     </row>
     <row r="32" ht="14" customHeight="1" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B32" s="2">
         <v>5</v>
@@ -9685,7 +9721,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B33" s="2">
         <v>7</v>
@@ -9707,10 +9743,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C36" s="2">
         <f>AVERAGE(C21:C33)</f>
@@ -9719,7 +9755,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B39" s="3">
         <v>4</v>
@@ -9730,7 +9766,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B40" s="3">
         <v>4</v>
@@ -9741,7 +9777,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B41" s="3">
         <v>5</v>
@@ -9762,10 +9798,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C44" s="3">
         <f>AVERAGE(C39:C41)</f>
@@ -9777,7 +9813,7 @@
         <v>22</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C47" s="4">
         <f>AVERAGE(C2:C15,C21:C33,C39:C41)</f>
@@ -9814,7 +9850,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -9825,7 +9861,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -9836,7 +9872,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -9847,7 +9883,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -9858,7 +9894,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -9869,7 +9905,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -9880,7 +9916,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -9891,7 +9927,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -9902,7 +9938,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
@@ -9913,7 +9949,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -9924,7 +9960,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
@@ -9935,7 +9971,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B13" s="1">
         <v>3</v>
@@ -9946,7 +9982,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1">
         <v>3</v>
@@ -9967,10 +10003,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17" s="1">
         <f>AVERAGE(C2:C14)</f>
@@ -9979,7 +10015,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -9990,7 +10026,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -10001,7 +10037,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
@@ -10012,7 +10048,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B23" s="2">
         <v>2</v>
@@ -10023,7 +10059,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2">
         <v>2</v>
@@ -10034,7 +10070,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2">
         <v>2</v>
@@ -10045,7 +10081,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B26" s="2">
         <v>2</v>
@@ -10056,7 +10092,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B27" s="2">
         <v>3</v>
@@ -10067,7 +10103,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B28" s="2">
         <v>3</v>
@@ -10079,7 +10115,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B29" s="2">
         <v>3</v>
@@ -10091,7 +10127,7 @@
     </row>
     <row r="30" ht="14" customHeight="1" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B30" s="2">
         <v>3</v>
@@ -10103,7 +10139,7 @@
     </row>
     <row r="31" ht="14" customHeight="1" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B31" s="2">
         <v>3</v>
@@ -10115,7 +10151,7 @@
     </row>
     <row r="32" ht="14" customHeight="1" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="B32" s="2">
         <v>4</v>
@@ -10127,7 +10163,7 @@
     </row>
     <row r="33" ht="14" customHeight="1" spans="1:5">
       <c r="A33" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B33" s="2">
         <v>5</v>
@@ -10139,7 +10175,7 @@
     </row>
     <row r="34" ht="14" customHeight="1" spans="1:5">
       <c r="A34" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B34" s="2">
         <v>7</v>
@@ -10161,10 +10197,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C37" s="2">
         <f>AVERAGE(C20:C34)</f>
@@ -10173,7 +10209,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B40" s="3">
         <v>4</v>
@@ -10184,7 +10220,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B41" s="3">
         <v>4</v>
@@ -10205,10 +10241,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C44" s="3">
         <f>AVERAGE(C40:C41)</f>
@@ -10220,7 +10256,7 @@
         <v>22</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C47" s="4">
         <f>AVERAGE(C2:C14,C20:C34,C40:C41)</f>
@@ -10257,7 +10293,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
@@ -10268,7 +10304,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -10279,7 +10315,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -10290,7 +10326,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -10301,7 +10337,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -10312,7 +10348,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -10323,7 +10359,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -10334,7 +10370,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -10345,7 +10381,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -10356,7 +10392,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -10367,7 +10403,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B12" s="1">
         <v>4</v>
@@ -10378,7 +10414,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B13" s="1">
         <v>4</v>
@@ -10389,7 +10425,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B14" s="1">
         <v>4</v>
@@ -10400,7 +10436,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1">
         <v>4</v>
@@ -10421,10 +10457,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C18" s="1">
         <f>AVERAGE(C2:C15)</f>
@@ -10433,7 +10469,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -10444,7 +10480,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
@@ -10455,7 +10491,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B23" s="2">
         <v>2</v>
@@ -10466,7 +10502,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2">
         <v>3</v>
@@ -10477,7 +10513,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B25" s="2">
         <v>3</v>
@@ -10488,7 +10524,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
@@ -10499,7 +10535,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B27" s="2">
         <v>3</v>
@@ -10510,7 +10546,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B28" s="2">
         <v>4</v>
@@ -10522,7 +10558,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B29" s="2">
         <v>4</v>
@@ -10534,7 +10570,7 @@
     </row>
     <row r="30" ht="14" customHeight="1" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B30" s="2">
         <v>5</v>
@@ -10546,7 +10582,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B31" s="2">
         <v>5</v>
@@ -10568,10 +10604,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C34" s="2">
         <f>AVERAGE(C21:C31)</f>
@@ -10580,7 +10616,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B37" s="3">
         <v>4</v>
@@ -10591,7 +10627,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B38" s="3">
         <v>4</v>
@@ -10602,7 +10638,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="3" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B39" s="3">
         <v>4</v>
@@ -10613,7 +10649,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B40" s="3">
         <v>5</v>
@@ -10624,7 +10660,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="3" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B41" s="3">
         <v>6</v>
@@ -10645,10 +10681,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C44" s="3">
         <f>AVERAGE(C37:C41)</f>
@@ -10657,7 +10693,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="B46" s="4" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:3">

--- a/src/views/game/zlzq/cardList/zz_myCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/zz_myCard/z_level.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11985" windowHeight="9795" activeTab="1"/>
+    <workbookView windowWidth="13185" windowHeight="11055" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="隐秘" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="509">
   <si>
     <t>名称</t>
   </si>
@@ -64,481 +64,490 @@
     <t>学仆-观测型2</t>
   </si>
   <si>
+    <t>沉重否定1</t>
+  </si>
+  <si>
+    <t>沉重否定2</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术1</t>
+  </si>
+  <si>
+    <t>克隆术2</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型1</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型2</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型3</t>
+  </si>
+  <si>
+    <t>符文·邪月之夜</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>No.5咒刃·布雷克</t>
+  </si>
+  <si>
+    <t>鬼童-7号</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>圣殿斥候</t>
+  </si>
+  <si>
+    <t>圣殿卫士</t>
+  </si>
+  <si>
+    <t>天使琼浆1</t>
+  </si>
+  <si>
+    <t>天使琼浆2</t>
+  </si>
+  <si>
+    <t>田园守望者</t>
+  </si>
+  <si>
+    <t>增援战线</t>
+  </si>
+  <si>
+    <t>符文·生命徽记</t>
+  </si>
+  <si>
+    <t>光明惩戒</t>
+  </si>
+  <si>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
+    <t>曙光·安娜贝尔</t>
+  </si>
+  <si>
+    <t>圣枪·卡洛琳</t>
+  </si>
+  <si>
+    <t>明日之音·露娜</t>
+  </si>
+  <si>
+    <t>正阳大主教·伊恩</t>
+  </si>
+  <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>帝国卡等：</t>
+  </si>
+  <si>
+    <t>心灵黑洞1</t>
+  </si>
+  <si>
+    <t>心灵黑洞2</t>
+  </si>
+  <si>
+    <t>心灵黑洞3</t>
+  </si>
+  <si>
+    <t>狡诈学徒1</t>
+  </si>
+  <si>
+    <t>狡诈学徒2</t>
+  </si>
+  <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>红海猎魔人</t>
+  </si>
+  <si>
+    <t>海神赐福1</t>
+  </si>
+  <si>
+    <t>海神赐福2</t>
+  </si>
+  <si>
+    <t>海神赐福3</t>
+  </si>
+  <si>
+    <t>海燕·鲍莉</t>
+  </si>
+  <si>
+    <t>魔卡幻术师·梅基</t>
+  </si>
+  <si>
+    <t>赤影·艾希尔</t>
+  </si>
+  <si>
+    <t>港口卡等：</t>
+  </si>
+  <si>
+    <t>飓风术1</t>
+  </si>
+  <si>
+    <t>飓风术2</t>
+  </si>
+  <si>
+    <t>飓风术3</t>
+  </si>
+  <si>
+    <t>长耳庄巧姑1</t>
+  </si>
+  <si>
+    <t>长耳庄巧姑2</t>
+  </si>
+  <si>
+    <t>连击1</t>
+  </si>
+  <si>
+    <t>连击2</t>
+  </si>
+  <si>
+    <t>铁山靠1</t>
+  </si>
+  <si>
+    <t>铁山靠2</t>
+  </si>
+  <si>
+    <t>风铃道人</t>
+  </si>
+  <si>
+    <t>驱魔道人</t>
+  </si>
+  <si>
+    <t>墨轩隐士</t>
+  </si>
+  <si>
+    <t>蟠桃会</t>
+  </si>
+  <si>
+    <t>万物之灵</t>
+  </si>
+  <si>
+    <t>神机玄女·轩</t>
+  </si>
+  <si>
+    <t>禅意卡等：</t>
+  </si>
+  <si>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>天使琼浆</t>
+  </si>
+  <si>
     <t>沉重否定</t>
   </si>
   <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术1</t>
-  </si>
-  <si>
-    <t>克隆术2</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型1</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型2</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型3</t>
-  </si>
-  <si>
-    <t>符文·邪月之夜</t>
+    <t>圣殿弩手</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>四芒军旗</t>
+  </si>
+  <si>
+    <t>克隆术</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>夺取阵地</t>
+  </si>
+  <si>
+    <t>花光春影·安娜贝尔</t>
+  </si>
+  <si>
+    <t>流星-7号</t>
+  </si>
+  <si>
+    <t>春花使者·卡洛琳</t>
+  </si>
+  <si>
+    <t>明日香·露娜</t>
+  </si>
+  <si>
+    <t>月之神·米拉</t>
+  </si>
+  <si>
+    <t>白袍·伊恩</t>
+  </si>
+  <si>
+    <t>总卡等：</t>
+  </si>
+  <si>
+    <t>武圣·云长</t>
+  </si>
+  <si>
+    <t>心灵黑洞</t>
+  </si>
+  <si>
+    <t>狡诈学徒</t>
+  </si>
+  <si>
+    <t>酗酒醉汉</t>
+  </si>
+  <si>
+    <t>占卜命运</t>
+  </si>
+  <si>
+    <t>走私狂徒</t>
+  </si>
+  <si>
+    <t>海神赐福</t>
+  </si>
+  <si>
+    <t>快乐使者</t>
+  </si>
+  <si>
+    <t>黑金诈术师</t>
+  </si>
+  <si>
+    <t>先发制人</t>
+  </si>
+  <si>
+    <t>学仆-猛禽型</t>
+  </si>
+  <si>
+    <t>黑水伏击</t>
+  </si>
+  <si>
+    <t>飓风术</t>
+  </si>
+  <si>
+    <t>长耳庄巧姑</t>
+  </si>
+  <si>
+    <t>连击</t>
+  </si>
+  <si>
+    <t>铁山靠</t>
+  </si>
+  <si>
+    <t>风卷残云</t>
+  </si>
+  <si>
+    <t>九天玄女·轩</t>
+  </si>
+  <si>
+    <t>上宝沁金耙</t>
+  </si>
+  <si>
+    <t>滑板少年·迪宁</t>
+  </si>
+  <si>
+    <t>种族</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>描述（20级数值）</t>
+  </si>
+  <si>
+    <t>帝国</t>
+  </si>
+  <si>
+    <t>蓝色</t>
+  </si>
+  <si>
+    <t>(22/18)：【洞察1】、【协战8】。</t>
+  </si>
+  <si>
+    <t>(25/30)：【洞察1】、【回命】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、英雄生命+66、抓一张牌、获得《真理石残片》。</t>
+  </si>
+  <si>
+    <t>大型弩车</t>
+  </si>
+  <si>
+    <t>(0/60)：【洞察1】、【协战25】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、召唤3个12/12民兵-lv17，75%概率再召唤一个。</t>
+  </si>
+  <si>
+    <t>塔楼弓手</t>
+  </si>
+  <si>
+    <t>(30/15)：【先攻】、洞察时:自身+6/+4、死亡:【洞察1】。</t>
+  </si>
+  <si>
+    <t>(20/28)：【洞察1】、洞察时:自身+5/+5，英雄获得生命（等同自身攻击）。</t>
+  </si>
+  <si>
+    <t>精英射手</t>
+  </si>
+  <si>
+    <t>(35/22)：【洞察1】、【先攻】、【协战9】。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、横排所有敌军受到150点伤害、50%概率获得《真理碎片》。</t>
+  </si>
+  <si>
+    <t>紫色</t>
+  </si>
+  <si>
+    <t>(20/32)：【洞察1】、命中英雄:召唤16/8警卫-lv15。</t>
+  </si>
+  <si>
+    <t>边境高墙</t>
+  </si>
+  <si>
+    <t>(0/85)：【守军】、【磐龙】、【护甲8】、回合结束:【洞察1】，若场上有冰封，自身生命+15。</t>
+  </si>
+  <si>
+    <t>冲锋装备</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、目标友军+27/+27、并获得【护甲14】。</t>
+  </si>
+  <si>
+    <t>圣殿卫队长</t>
+  </si>
+  <si>
+    <t>(30/60)：【回命】、命中英雄:召唤16/21圣殿卫士-lv16。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、将横排敌军移回玩家手上、友军横排召唤21/9警卫-lv18。</t>
+  </si>
+  <si>
+    <t>召集护卫</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、在目标位置和随机位置，召唤3/60圣堂门卫-lv20、护甲友军攻击+12，获得【磐龙】1回合。</t>
+  </si>
+  <si>
+    <t>皇家射手</t>
+  </si>
+  <si>
+    <t>(40/20)：【先攻】、【洞察1】、回合开始:召唤25/12塔楼弓手-lv18（次数上限：3）。</t>
+  </si>
+  <si>
+    <t>(40/80)：【回命】、【洞察3】、登场:消灭对面横排首位新进场敌军。</t>
+  </si>
+  <si>
+    <t>禁卫指挥官</t>
+  </si>
+  <si>
+    <t>(30/54)：【洞察1】、【护甲8】、洞察时：全体友军+6/+6。</t>
+  </si>
+  <si>
+    <t>橙色</t>
+  </si>
+  <si>
+    <t>(20/32)：【洞察2】、攻击前:所有友军+6/+6，魔防+3。（皮肤：命中时：另一友军+1/+1。）</t>
+  </si>
+  <si>
+    <t>百花长枪·卡洛琳</t>
+  </si>
+  <si>
+    <t>(36/36)：【回命】、【神佑】、【护甲15】。（皮肤：命中时：【洞察1】，50几率英雄生命额外+10。）</t>
+  </si>
+  <si>
+    <t>(0/20)：【魔防20】、同横排其他单位不会攻击（无视神佑和魔免）、回合结束:【洞察1】、另一友军+7/+15。（皮肤：登场：其他全体友军，攻击+3，本回合护甲+X（X等同露娜等级）。）</t>
+  </si>
+  <si>
+    <t>(20/70)：登场:英雄生命+70、英雄获得生命:回复效果加倍，自身+3/+13，其他友军+4/+4。（皮肤：【洞察1】、洞察时：自身魔防+2，其他友军攻击+1。）</t>
+  </si>
+  <si>
+    <t>隐秘</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、英雄生命+30。</t>
+  </si>
+  <si>
+    <t>方尖魔碑</t>
+  </si>
+  <si>
+    <t>(0/40)：【守军】、敌方法力上限-1、回合结束:70%几率【洞察1】。</t>
+  </si>
+  <si>
+    <t>(22/32)：洞察时：自身+4/+4、死亡：【洞察1】，英雄恢复生命（等同攻击力）。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、横排敌军攻击-33。</t>
+  </si>
+  <si>
+    <t>学仆-渗透型</t>
+  </si>
+  <si>
+    <t>(35/35)：【洞察1】、【穿透】、【护甲8】。</t>
+  </si>
+  <si>
+    <t>请示隐秘者</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、抽2张牌、随机友军生命+66、充能:多抽一张牌。</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、目标单位+23/+23，获得【隐形】。</t>
+  </si>
+  <si>
+    <t>(21/27)：【洞察1】、登场:沉默随机敌军、命中时:65%几率【洞察1】、回合结束:35%几率沉默随机敌军。</t>
+  </si>
+  <si>
+    <t>(法术)：【洞察1】、复制目标单位到手上，英雄生命+40。</t>
+  </si>
+  <si>
+    <t>神秘学教授</t>
+  </si>
+  <si>
+    <t>(13/33)：每当一个敌军死亡:获得【洞悉之眼-lv20】（每次对战仅可触发3次）。</t>
+  </si>
+  <si>
+    <t>(27/15)：【先攻】、命中时：【洞察1】、洞察时：全体先攻友军攻击+9。</t>
+  </si>
+  <si>
+    <t>(16/30)：【洞察1】、洞察时：自身+3/+8，射击英雄。</t>
   </si>
   <si>
     <t>白首魔根</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>No.5咒刃·布雷克</t>
-  </si>
-  <si>
-    <t>鬼童-7号</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
-    <t>圣殿斥候</t>
-  </si>
-  <si>
-    <t>圣殿卫士</t>
-  </si>
-  <si>
-    <t>天使琼浆1</t>
-  </si>
-  <si>
-    <t>天使琼浆2</t>
-  </si>
-  <si>
-    <t>田园守望者</t>
-  </si>
-  <si>
-    <t>增援战线</t>
-  </si>
-  <si>
-    <t>光明惩戒</t>
-  </si>
-  <si>
-    <t>圣殿御卫</t>
-  </si>
-  <si>
-    <t>夺取阵地</t>
-  </si>
-  <si>
-    <t>惩戒天使</t>
-  </si>
-  <si>
-    <t>曙光·安娜贝尔</t>
-  </si>
-  <si>
-    <t>圣枪·卡洛琳</t>
-  </si>
-  <si>
-    <t>明日之音·露娜</t>
-  </si>
-  <si>
-    <t>正阳大主教·伊恩</t>
-  </si>
-  <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>帝国卡等：</t>
-  </si>
-  <si>
-    <t>心灵黑洞1</t>
-  </si>
-  <si>
-    <t>心灵黑洞2</t>
-  </si>
-  <si>
-    <t>心灵黑洞3</t>
-  </si>
-  <si>
-    <t>狡诈学徒1</t>
-  </si>
-  <si>
-    <t>狡诈学徒2</t>
-  </si>
-  <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>不法交易</t>
-  </si>
-  <si>
-    <t>红海猎魔人</t>
-  </si>
-  <si>
-    <t>海神赐福1</t>
-  </si>
-  <si>
-    <t>海神赐福2</t>
-  </si>
-  <si>
-    <t>海神赐福3</t>
-  </si>
-  <si>
-    <t>海燕·鲍莉</t>
-  </si>
-  <si>
-    <t>魔卡幻术师·梅基</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
-  </si>
-  <si>
-    <t>港口卡等：</t>
-  </si>
-  <si>
-    <t>飓风术1</t>
-  </si>
-  <si>
-    <t>飓风术2</t>
-  </si>
-  <si>
-    <t>飓风术3</t>
-  </si>
-  <si>
-    <t>长耳庄巧姑1</t>
-  </si>
-  <si>
-    <t>长耳庄巧姑2</t>
-  </si>
-  <si>
-    <t>连击1</t>
-  </si>
-  <si>
-    <t>连击2</t>
-  </si>
-  <si>
-    <t>铁山靠1</t>
-  </si>
-  <si>
-    <t>铁山靠2</t>
-  </si>
-  <si>
-    <t>风铃道人</t>
-  </si>
-  <si>
-    <t>驱魔道人</t>
-  </si>
-  <si>
-    <t>墨轩隐士</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>万物之灵</t>
-  </si>
-  <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
-    <t>禅意卡等：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>天使琼浆</t>
-  </si>
-  <si>
-    <t>圣殿弩手</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>四芒军旗</t>
-  </si>
-  <si>
-    <t>克隆术</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
-    <t>花光春影·安娜贝尔</t>
-  </si>
-  <si>
-    <t>流星-7号</t>
-  </si>
-  <si>
-    <t>春花使者·卡洛琳</t>
-  </si>
-  <si>
-    <t>明日香·露娜</t>
-  </si>
-  <si>
-    <t>月之神·米拉</t>
-  </si>
-  <si>
-    <t>白袍·伊恩</t>
-  </si>
-  <si>
-    <t>总卡等：</t>
-  </si>
-  <si>
-    <t>武圣·云长</t>
-  </si>
-  <si>
-    <t>心灵黑洞</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
-  </si>
-  <si>
-    <t>酗酒醉汉</t>
-  </si>
-  <si>
-    <t>占卜命运</t>
-  </si>
-  <si>
-    <t>走私狂徒</t>
-  </si>
-  <si>
-    <t>海神赐福</t>
-  </si>
-  <si>
-    <t>快乐使者</t>
-  </si>
-  <si>
-    <t>黑金诈术师</t>
-  </si>
-  <si>
-    <t>先发制人</t>
-  </si>
-  <si>
-    <t>学仆-猛禽型</t>
-  </si>
-  <si>
-    <t>黑水伏击</t>
-  </si>
-  <si>
-    <t>飓风术</t>
-  </si>
-  <si>
-    <t>长耳庄巧姑</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>铁山靠</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>九天玄女·轩</t>
-  </si>
-  <si>
-    <t>上宝沁金耙</t>
-  </si>
-  <si>
-    <t>滑板少年·迪宁</t>
-  </si>
-  <si>
-    <t>种族</t>
-  </si>
-  <si>
-    <t>品质</t>
-  </si>
-  <si>
-    <t>描述（20级数值）</t>
-  </si>
-  <si>
-    <t>帝国</t>
-  </si>
-  <si>
-    <t>蓝色</t>
-  </si>
-  <si>
-    <t>(22/18)：【洞察1】、【协战8】。</t>
-  </si>
-  <si>
-    <t>(25/30)：【洞察1】、【回命】。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、英雄生命+66、抓一张牌、获得《真理石残片》。</t>
-  </si>
-  <si>
-    <t>大型弩车</t>
-  </si>
-  <si>
-    <t>(0/60)：【洞察1】、【协战25】。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、召唤3个12/12民兵-lv17，75%概率再召唤一个。</t>
-  </si>
-  <si>
-    <t>塔楼弓手</t>
-  </si>
-  <si>
-    <t>(30/15)：【先攻】、洞察时:自身+6/+4、死亡:【洞察1】。</t>
-  </si>
-  <si>
-    <t>(20/28)：【洞察1】、洞察时:自身+5/+5，英雄获得生命（等同自身攻击）。</t>
-  </si>
-  <si>
-    <t>精英射手</t>
-  </si>
-  <si>
-    <t>(35/22)：【洞察1】、【先攻】、【协战9】。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、横排所有敌军受到150点伤害、50%概率获得《真理碎片》。</t>
-  </si>
-  <si>
-    <t>紫色</t>
-  </si>
-  <si>
-    <t>(20/32)：【洞察1】、命中英雄:召唤16/8警卫-lv15。</t>
-  </si>
-  <si>
-    <t>边境高墙</t>
-  </si>
-  <si>
-    <t>(0/85)：【守军】、【磐龙】、【护甲8】、回合结束:【洞察1】，若场上有冰封，自身生命+15。</t>
-  </si>
-  <si>
-    <t>冲锋装备</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、目标友军+27/+27、并获得【护甲14】。</t>
-  </si>
-  <si>
-    <t>圣殿卫队长</t>
-  </si>
-  <si>
-    <t>(30/60)：【回命】、命中英雄:召唤16/21圣殿卫士-lv16。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、将横排敌军移回玩家手上、友军横排召唤21/9警卫-lv18。</t>
-  </si>
-  <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、在目标位置和随机位置，召唤3/60圣堂门卫-lv20、护甲友军攻击+12，获得【磐龙】1回合。</t>
-  </si>
-  <si>
-    <t>皇家射手</t>
-  </si>
-  <si>
-    <t>(40/20)：【先攻】、【洞察1】、回合开始:召唤25/12塔楼弓手-lv18（次数上限：3）。</t>
-  </si>
-  <si>
-    <t>(40/80)：【回命】、【洞察3】、登场:消灭对面横排首位新进场敌军。</t>
-  </si>
-  <si>
-    <t>禁卫指挥官</t>
-  </si>
-  <si>
-    <t>(30/54)：【洞察1】、【护甲8】、洞察时：全体友军+6/+6。</t>
-  </si>
-  <si>
-    <t>橙色</t>
-  </si>
-  <si>
-    <t>(20/32)：【洞察2】、攻击前:所有友军+6/+6，魔防+3。（皮肤：命中时：另一友军+1/+1。）</t>
-  </si>
-  <si>
-    <t>百花长枪·卡洛琳</t>
-  </si>
-  <si>
-    <t>(36/36)：【回命】、【神佑】、【护甲15】。（皮肤：命中时：【洞察1】，50几率英雄生命额外+10。）</t>
-  </si>
-  <si>
-    <t>(0/20)：【魔防20】、同横排其他单位不会攻击（无视神佑和魔免）、回合结束:【洞察1】、另一友军+7/+15。（皮肤：登场：其他全体友军，攻击+3，本回合护甲+X（X等同露娜等级）。）</t>
-  </si>
-  <si>
-    <t>(20/70)：登场:英雄生命+70、英雄获得生命:回复效果加倍，自身+3/+13，其他友军+4/+4。（皮肤：【洞察1】、洞察时：自身魔防+2，其他友军攻击+1。）</t>
-  </si>
-  <si>
-    <t>隐秘</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、英雄生命+30。</t>
-  </si>
-  <si>
-    <t>方尖魔碑</t>
-  </si>
-  <si>
-    <t>(0/40)：【守军】、敌方法力上限-1、回合结束:70%几率【洞察1】。</t>
-  </si>
-  <si>
-    <t>(22/32)：洞察时：自身+4/+4、死亡：【洞察1】，英雄恢复生命（等同攻击力）。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、横排敌军攻击-33。</t>
-  </si>
-  <si>
-    <t>学仆-渗透型</t>
-  </si>
-  <si>
-    <t>(35/35)：【洞察1】、【穿透】、【护甲8】。</t>
-  </si>
-  <si>
-    <t>请示隐秘者</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、抽2张牌、随机友军生命+66、充能:多抽一张牌。</t>
-  </si>
-  <si>
-    <t>隐形术</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、目标单位+23/+23，获得【隐形】。</t>
-  </si>
-  <si>
-    <t>(21/27)：【洞察1】、登场:沉默随机敌军、命中时:65%几率【洞察1】、回合结束:35%几率沉默随机敌军。</t>
-  </si>
-  <si>
-    <t>(法术)：【洞察1】、复制目标单位到手上，英雄生命+40。</t>
-  </si>
-  <si>
-    <t>神秘学教授</t>
-  </si>
-  <si>
-    <t>(13/33)：每当一个敌军死亡:获得【洞悉之眼-lv20】（每次对战仅可触发3次）。</t>
-  </si>
-  <si>
-    <t>(27/15)：【先攻】、命中时：【洞察1】、洞察时：全体先攻友军攻击+9。</t>
-  </si>
-  <si>
-    <t>(16/30)：【洞察1】、洞察时：自身+3/+8，射击英雄。</t>
   </si>
   <si>
     <t>(17/67)：【洞察1】、【魔免】、回合结束:自身攻击加倍。</t>
@@ -2562,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2595,13 +2604,19 @@
         <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>19</v>
+      </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1"/>
@@ -2609,26 +2624,20 @@
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>23</v>
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>20.8</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2639,7 +2648,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2650,7 +2659,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2658,10 +2667,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2683,7 +2692,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2694,7 +2703,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2702,10 +2711,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2742,14 +2751,14 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="2">
-        <f>AVERAGE(C11:C20)</f>
-        <v>20</v>
+        <f>AVERAGE(C12:C20)</f>
+        <v>20.5555555555556</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2771,7 +2780,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2797,14 +2806,14 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C31" s="3">
         <f>AVERAGE(C26:C28)</f>
-        <v>21.6666666666667</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -2815,8 +2824,8 @@
         <v>24</v>
       </c>
       <c r="C34" s="4">
-        <f>AVERAGE(C2:C5,C11:C20,C26:C28)</f>
-        <v>20.7647058823529</v>
+        <f>AVERAGE(C2:C6,C12:C20,C26:C28)</f>
+        <v>20.8823529411765</v>
       </c>
     </row>
   </sheetData>
@@ -2840,19 +2849,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2860,2365 +2869,2365 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D10">
         <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D11">
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12">
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D20">
         <v>6</v>
       </c>
       <c r="E20" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D21">
         <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D23">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D24">
         <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B29" t="s">
         <v>74</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D29">
         <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D30">
         <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D34">
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B36" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>167</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B41" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D42">
         <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B43" t="s">
         <v>18</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D43">
         <v>7</v>
       </c>
       <c r="E43" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D44">
         <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D45">
         <v>6</v>
       </c>
       <c r="E45" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D48">
         <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D49">
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B50" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D50">
         <v>2</v>
       </c>
       <c r="E50" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D51">
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D52">
         <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s">
         <v>67</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D53">
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B54" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D54">
         <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B55" t="s">
         <v>68</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D55">
         <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B56" t="s">
         <v>69</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D56">
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B57" t="s">
         <v>70</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D57">
         <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B58" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D58">
         <v>5</v>
       </c>
       <c r="E58" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B59" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D59">
         <v>4</v>
       </c>
       <c r="E59" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B63" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D63">
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B64" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D64">
         <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B65" t="s">
         <v>47</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D65">
         <v>2</v>
       </c>
       <c r="E65" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B66" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D66">
         <v>2</v>
       </c>
       <c r="E66" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B67" t="s">
         <v>48</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D67">
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B68" t="s">
         <v>49</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D68">
         <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D69">
         <v>2</v>
       </c>
       <c r="E69" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B70" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D70">
         <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B71" t="s">
         <v>50</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D71">
         <v>2</v>
       </c>
       <c r="E71" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B72" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D72">
         <v>2</v>
       </c>
       <c r="E72" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B73" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D73">
         <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B74" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D74">
         <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B75" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D75">
         <v>4</v>
       </c>
       <c r="E75" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B78" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D78">
         <v>2</v>
       </c>
       <c r="E78" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B79" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D79">
         <v>2</v>
       </c>
       <c r="E79" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B80" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D80">
         <v>3</v>
       </c>
       <c r="E80" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B81" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D81">
         <v>4</v>
       </c>
       <c r="E81" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B82" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D82">
         <v>3</v>
       </c>
       <c r="E82" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B83" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D83">
         <v>5</v>
       </c>
       <c r="E83" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B86" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B87" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D87">
         <v>2</v>
       </c>
       <c r="E87" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B88" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D88">
         <v>2</v>
       </c>
       <c r="E88" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B89" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D89">
         <v>2</v>
       </c>
       <c r="E89" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B90" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D90">
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B91" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D91">
         <v>3</v>
       </c>
       <c r="E91" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B92" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D92">
         <v>3</v>
       </c>
       <c r="E92" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B93" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D93">
         <v>3</v>
       </c>
       <c r="E93" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B94" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D94">
         <v>4</v>
       </c>
       <c r="E94" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B95" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D95">
         <v>4</v>
       </c>
       <c r="E95" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B96" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D96">
         <v>4</v>
       </c>
       <c r="E96" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B97" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D97">
         <v>5</v>
       </c>
       <c r="E97" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B98" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D98">
         <v>5</v>
       </c>
       <c r="E98" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B99" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D99">
         <v>2</v>
       </c>
       <c r="E99" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B100" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D100">
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B101" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D101">
         <v>3</v>
       </c>
       <c r="E101" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B102" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D102">
         <v>4</v>
       </c>
       <c r="E102" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B105" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D105">
         <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B106" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D106">
         <v>2</v>
       </c>
       <c r="E106" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B107" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D107">
         <v>3</v>
       </c>
       <c r="E107" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B108" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D108">
         <v>3</v>
       </c>
       <c r="E108" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B109" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D109">
         <v>2</v>
       </c>
       <c r="E109" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B110" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D110">
         <v>3</v>
       </c>
       <c r="E110" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B111" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D111">
         <v>4</v>
       </c>
       <c r="E111" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B112" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D112">
         <v>6</v>
       </c>
       <c r="E112" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B117" t="s">
         <v>0</v>
       </c>
       <c r="C117" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D117" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E117" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B118" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D118" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E118" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B119" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D119" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E119" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B120" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E120" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B121" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E121" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B122" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D122" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E122" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B123" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D123" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E123" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B124" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D124" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E124" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B125" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D125" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E125" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B126" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D126" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E126" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B127" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D127" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E127" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B128" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D128" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E128" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B129" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D129" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E129" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B130" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D130" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E130" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E131" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B132" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D132" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E132" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B133" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D133" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E133" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B134" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D134" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E134" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B135" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D135" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E135" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B136" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E136" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B137" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E137" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B138" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D138" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E138" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B139" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D139" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E139" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B140" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D140" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E140" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B141" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D141" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E141" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B142" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D142" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E142" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B143" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D143" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E143" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B144" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D144" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E144" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B145" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D145" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E145" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B146" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D146" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E146" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B147" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E147" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B148" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D148" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E148" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B149" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D149" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E149" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B150" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D150" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E150" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B151" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D151" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E151" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B152" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D152" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E152" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B153" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D153" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E153" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B154" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D154" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E154" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B155" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D155" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E155" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B156" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D156" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E156" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B157" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D157" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E157" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -5242,1124 +5251,1124 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B5" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B11" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B18" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D20">
         <v>6</v>
       </c>
       <c r="E20" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D21">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B22" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B23" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D23">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B24" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D24">
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B26" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D26">
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D27">
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B28" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D28">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D32">
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D33">
         <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D34">
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B35" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B36" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D36">
         <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B37" t="s">
         <v>18</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D37">
         <v>7</v>
       </c>
       <c r="E37" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B38" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D38">
         <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B39" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D39">
         <v>2</v>
       </c>
       <c r="E39" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s">
         <v>20</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D40">
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B43" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D43">
         <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B44" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D44">
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B45" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D45">
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B46" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D46">
         <v>4</v>
       </c>
       <c r="E46" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B47" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D47">
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B48" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D48">
         <v>6</v>
       </c>
       <c r="E48" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D49">
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B50" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D50">
         <v>6</v>
       </c>
       <c r="E50" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B53" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D53">
         <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B54" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D54">
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B57" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D57">
         <v>2</v>
       </c>
       <c r="E57" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B58" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D58">
         <v>4</v>
       </c>
       <c r="E58" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B59" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D59">
         <v>2</v>
       </c>
       <c r="E59" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B60" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D60">
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:5">
       <c r="A61" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B61" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D61">
         <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:5">
       <c r="A62" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B62" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D62">
         <v>5</v>
       </c>
       <c r="E62" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:5">
       <c r="A63" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B63" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D63">
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:5">
       <c r="A64" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B64" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D64">
         <v>4</v>
       </c>
       <c r="E64" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:5">
       <c r="A65" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B65" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D65">
         <v>5</v>
       </c>
       <c r="E65" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B68" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D68">
         <v>2</v>
       </c>
       <c r="E68" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B69" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D69">
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B72" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D72">
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B73" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D73">
         <v>4</v>
       </c>
       <c r="E73" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B74" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D74">
         <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B75" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D75">
         <v>5</v>
       </c>
       <c r="E75" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B76" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D76">
         <v>5</v>
       </c>
       <c r="E76" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B77" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D77">
         <v>5</v>
       </c>
       <c r="E77" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B78" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D78">
         <v>6</v>
       </c>
       <c r="E78" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -6388,33 +6397,33 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="E1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="G1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C2" s="1">
         <v>18</v>
@@ -6427,15 +6436,15 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C3" s="1">
         <v>2</v>
@@ -6448,10 +6457,10 @@
         <v>2684</v>
       </c>
       <c r="F3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G3" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -6459,7 +6468,7 @@
         <v>75</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C4" s="1">
         <v>17</v>
@@ -6474,10 +6483,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C5" s="1">
         <v>18</v>
@@ -6492,10 +6501,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C6" s="1">
         <v>18</v>
@@ -6510,10 +6519,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
@@ -6526,7 +6535,7 @@
         <v>2640</v>
       </c>
       <c r="F7" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -6534,7 +6543,7 @@
         <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C8" s="1">
         <v>16</v>
@@ -6549,10 +6558,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C9" s="1">
         <v>16</v>
@@ -6567,10 +6576,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C10" s="1">
         <v>16</v>
@@ -6585,10 +6594,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C11" s="1">
         <v>6</v>
@@ -6603,10 +6612,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2">
         <v>18</v>
@@ -6619,15 +6628,15 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
@@ -6642,10 +6651,10 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C14" s="2">
         <v>17</v>
@@ -6660,10 +6669,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C15" s="2">
         <v>15</v>
@@ -6678,10 +6687,10 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C16" s="2">
         <v>14</v>
@@ -6694,15 +6703,15 @@
         <v>955</v>
       </c>
       <c r="F16" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C17" s="2">
         <v>16</v>
@@ -6720,7 +6729,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C18" s="2">
         <v>15</v>
@@ -6735,10 +6744,10 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C19" s="2">
         <v>4</v>
@@ -6753,10 +6762,10 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C20" s="2">
         <v>4</v>
@@ -6771,10 +6780,10 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -6789,10 +6798,10 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C22" s="2">
         <v>7</v>
@@ -6807,10 +6816,10 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C23" s="2">
         <v>5</v>
@@ -6828,7 +6837,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C24" s="3">
         <v>13</v>
@@ -6841,15 +6850,15 @@
         <v>552</v>
       </c>
       <c r="F24" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C25" s="3">
         <v>16</v>
@@ -6862,7 +6871,7 @@
         <v>382</v>
       </c>
       <c r="F25" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -6870,7 +6879,7 @@
         <v>37</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C26" s="3">
         <v>13</v>
@@ -6883,7 +6892,7 @@
         <v>726</v>
       </c>
       <c r="F26" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -6891,7 +6900,7 @@
         <v>38</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C27" s="3">
         <v>15</v>
@@ -6904,7 +6913,7 @@
         <v>470</v>
       </c>
       <c r="F27" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -6912,7 +6921,7 @@
         <v>39</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C28" s="3">
         <v>14</v>
@@ -6925,15 +6934,15 @@
         <v>629</v>
       </c>
       <c r="F28" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C29" s="3">
         <v>2</v>
@@ -6951,7 +6960,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -6964,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -6972,7 +6981,7 @@
         <v>5</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C35" s="1">
         <v>16</v>
@@ -6987,10 +6996,10 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="C36" s="1">
         <v>17</v>
@@ -7003,15 +7012,15 @@
         <v>149</v>
       </c>
       <c r="F36" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C37" s="1">
         <v>13</v>
@@ -7024,15 +7033,15 @@
         <v>1648</v>
       </c>
       <c r="F37" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C38" s="1">
         <v>13</v>
@@ -7045,15 +7054,15 @@
         <v>1856</v>
       </c>
       <c r="F38" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C39" s="1">
         <v>18</v>
@@ -7066,15 +7075,15 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C40" s="1">
         <v>6</v>
@@ -7089,10 +7098,10 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C41" s="1">
         <v>6</v>
@@ -7107,10 +7116,10 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C42" s="2">
         <v>14</v>
@@ -7123,15 +7132,15 @@
         <v>1105</v>
       </c>
       <c r="F42" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C43" s="2">
         <v>16</v>
@@ -7144,15 +7153,15 @@
         <v>438</v>
       </c>
       <c r="F43" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C44" s="2">
         <v>14</v>
@@ -7165,15 +7174,15 @@
         <v>911</v>
       </c>
       <c r="F44" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C45" s="2">
         <v>17</v>
@@ -7186,18 +7195,18 @@
         <v>279</v>
       </c>
       <c r="F45" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G45" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C46" s="2">
         <v>17</v>
@@ -7210,15 +7219,15 @@
         <v>320</v>
       </c>
       <c r="F46" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -7233,10 +7242,10 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C48" s="2">
         <v>15</v>
@@ -7254,7 +7263,7 @@
         <v>17</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C49" s="2">
         <v>13</v>
@@ -7272,7 +7281,7 @@
         <v>18</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C50" s="2">
         <v>17</v>
@@ -7285,15 +7294,15 @@
         <v>320</v>
       </c>
       <c r="F50" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C51" s="2">
         <v>10</v>
@@ -7306,15 +7315,15 @@
         <v>953</v>
       </c>
       <c r="F51" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="3" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C52" s="3">
         <v>3</v>
@@ -7332,7 +7341,7 @@
         <v>21</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C53" s="3">
         <v>2</v>
@@ -7350,7 +7359,7 @@
         <v>22</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C54" s="3">
         <v>12</v>
@@ -7363,15 +7372,15 @@
         <v>477</v>
       </c>
       <c r="F54" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C55" s="3">
         <v>6</v>
@@ -7386,10 +7395,10 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="3" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C56" s="3">
         <v>3</v>
@@ -7422,16 +7431,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7772,7 +7781,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7813,16 +7822,22 @@
         <v>31</v>
       </c>
       <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C9" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1"/>
@@ -7830,38 +7845,32 @@
       <c r="C10" s="1"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>22</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1">
+        <f>AVERAGE(C2:C9)</f>
+        <v>21.125</v>
+      </c>
+      <c r="D12" s="2"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -7887,14 +7896,14 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="2">
-        <f>AVERAGE(C14:C16)</f>
-        <v>21.3333333333333</v>
+        <f>AVERAGE(C15:C16)</f>
+        <v>22.5</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7905,7 +7914,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7938,7 +7947,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7949,7 +7958,7 @@
         <v>8</v>
       </c>
       <c r="C26" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -7964,14 +7973,14 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C22:C26)</f>
-        <v>20.8</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7982,8 +7991,8 @@
         <v>41</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C8,C14:C16,C22:C26)</f>
-        <v>21.4666666666667</v>
+        <f>AVERAGE(C2:C9,C15:C16,C22:C26)</f>
+        <v>21.4</v>
       </c>
     </row>
   </sheetData>
@@ -8114,10 +8123,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1">
         <f>AVERAGE(C2:C9)</f>
@@ -8180,7 +8189,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>19</v>
@@ -8235,7 +8244,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>40</v>
@@ -8407,10 +8416,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1">
         <f>AVERAGE(C2:C11)</f>
@@ -8473,7 +8482,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>19</v>
@@ -8506,7 +8515,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>40</v>
@@ -8624,7 +8633,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -8635,7 +8644,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -8668,7 +8677,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
@@ -8679,7 +8688,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>5</v>
@@ -8700,10 +8709,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="1">
         <f>AVERAGE(C2:C13)</f>
@@ -8712,7 +8721,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -8723,7 +8732,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -8734,7 +8743,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -8745,7 +8754,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
@@ -8756,7 +8765,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23" s="2">
         <v>2</v>
@@ -8767,7 +8776,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="2">
         <v>3</v>
@@ -8778,7 +8787,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B25" s="2">
         <v>3</v>
@@ -8789,7 +8798,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
@@ -8800,7 +8809,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2">
         <v>4</v>
@@ -8854,7 +8863,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>19</v>
@@ -8866,7 +8875,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B36" s="3">
         <v>3</v>
@@ -8877,7 +8886,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B37" s="3">
         <v>4</v>
@@ -8888,7 +8897,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B38" s="3">
         <v>4</v>
@@ -8899,7 +8908,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B39" s="3">
         <v>4</v>
@@ -8910,7 +8919,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B40" s="3">
         <v>5</v>
@@ -8921,7 +8930,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B41" s="3">
         <v>6</v>
@@ -8942,7 +8951,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>40</v>
@@ -8957,7 +8966,7 @@
         <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C47">
         <f>AVERAGE(C2:C13,C19:C30,C36:C41)</f>
@@ -9061,7 +9070,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -9072,7 +9081,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -9105,7 +9114,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
@@ -9116,7 +9125,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1">
         <v>5</v>
@@ -9137,10 +9146,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="1">
         <f>AVERAGE(C2:C13)</f>
@@ -9149,7 +9158,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="2">
         <v>1</v>
@@ -9160,7 +9169,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -9171,7 +9180,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -9182,7 +9191,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
@@ -9193,7 +9202,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23" s="2">
         <v>2</v>
@@ -9204,7 +9213,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="2">
         <v>3</v>
@@ -9215,7 +9224,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B25" s="2">
         <v>3</v>
@@ -9226,7 +9235,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
@@ -9237,7 +9246,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2">
         <v>4</v>
@@ -9282,7 +9291,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>19</v>
@@ -9294,7 +9303,7 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B35" s="3">
         <v>3</v>
@@ -9305,7 +9314,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B36" s="3">
         <v>4</v>
@@ -9316,7 +9325,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B37" s="3">
         <v>4</v>
@@ -9327,7 +9336,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B38" s="3">
         <v>4</v>
@@ -9338,7 +9347,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B39" s="3">
         <v>5</v>
@@ -9349,7 +9358,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B40" s="3">
         <v>6</v>
@@ -9360,7 +9369,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B41" s="3">
         <v>8</v>
@@ -9381,7 +9390,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>40</v>
@@ -9396,7 +9405,7 @@
         <v>23</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C47" s="4">
         <f>AVERAGE(C2:C13,C19:C29,C35:C41)</f>
@@ -9456,7 +9465,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -9467,7 +9476,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -9500,7 +9509,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -9522,7 +9531,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
@@ -9533,7 +9542,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -9555,7 +9564,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B13" s="1">
         <v>3</v>
@@ -9577,7 +9586,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B15" s="1">
         <v>3</v>
@@ -9598,10 +9607,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="1">
         <f>AVERAGE(C2:C15)</f>
@@ -9610,7 +9619,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -9632,7 +9641,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23" s="2">
         <v>2</v>
@@ -9643,7 +9652,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="2">
         <v>2</v>
@@ -9654,7 +9663,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2">
         <v>2</v>
@@ -9665,7 +9674,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B26" s="2">
         <v>2</v>
@@ -9676,7 +9685,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B27" s="2">
         <v>2</v>
@@ -9687,7 +9696,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="2">
         <v>3</v>
@@ -9698,7 +9707,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2">
         <v>3</v>
@@ -9710,7 +9719,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B30" s="2">
         <v>3</v>
@@ -9722,7 +9731,7 @@
     </row>
     <row r="31" ht="14" customHeight="1" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B31" s="2">
         <v>4</v>
@@ -9768,7 +9777,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>19</v>
@@ -9780,7 +9789,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B39" s="3">
         <v>4</v>
@@ -9802,7 +9811,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B41" s="3">
         <v>5</v>
@@ -9823,7 +9832,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>40</v>
@@ -9838,7 +9847,7 @@
         <v>23</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C47" s="4">
         <f>AVERAGE(C2:C15,C21:C33,C39:C41)</f>
@@ -9886,7 +9895,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -9897,7 +9906,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -9908,7 +9917,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
@@ -9941,7 +9950,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -9963,7 +9972,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
@@ -9974,7 +9983,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -9996,7 +10005,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B13" s="1">
         <v>3</v>
@@ -10028,10 +10037,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="1">
         <f>AVERAGE(C2:C14)</f>
@@ -10040,7 +10049,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20" s="2">
         <v>2</v>
@@ -10062,7 +10071,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
@@ -10073,7 +10082,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23" s="2">
         <v>2</v>
@@ -10084,7 +10093,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B24" s="2">
         <v>2</v>
@@ -10095,7 +10104,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B25" s="2">
         <v>2</v>
@@ -10106,7 +10115,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2">
         <v>2</v>
@@ -10117,7 +10126,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B27" s="2">
         <v>3</v>
@@ -10128,7 +10137,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="2">
         <v>3</v>
@@ -10140,7 +10149,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2">
         <v>3</v>
@@ -10152,7 +10161,7 @@
     </row>
     <row r="30" ht="14" customHeight="1" spans="1:5">
       <c r="A30" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B30" s="2">
         <v>3</v>
@@ -10164,7 +10173,7 @@
     </row>
     <row r="31" ht="14" customHeight="1" spans="1:5">
       <c r="A31" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B31" s="2">
         <v>3</v>
@@ -10176,7 +10185,7 @@
     </row>
     <row r="32" ht="14" customHeight="1" spans="1:5">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B32" s="2">
         <v>4</v>
@@ -10222,7 +10231,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>19</v>
@@ -10234,7 +10243,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B40" s="3">
         <v>4</v>
@@ -10266,7 +10275,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>40</v>
@@ -10281,7 +10290,7 @@
         <v>23</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C47" s="4">
         <f>AVERAGE(C2:C14,C20:C34,C40:C41)</f>
@@ -10351,7 +10360,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -10362,7 +10371,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -10373,7 +10382,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -10384,7 +10393,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -10395,7 +10404,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -10406,7 +10415,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -10417,7 +10426,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
@@ -10439,7 +10448,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B13" s="1">
         <v>4</v>
@@ -10450,7 +10459,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B14" s="1">
         <v>4</v>
@@ -10461,7 +10470,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B15" s="1">
         <v>4</v>
@@ -10482,10 +10491,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="1">
         <f>AVERAGE(C2:C15)</f>
@@ -10494,7 +10503,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21" s="2">
         <v>2</v>
@@ -10505,7 +10514,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B22" s="2">
         <v>2</v>
@@ -10516,7 +10525,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23" s="2">
         <v>2</v>
@@ -10527,7 +10536,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="2">
         <v>3</v>
@@ -10538,7 +10547,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B25" s="2">
         <v>3</v>
@@ -10549,7 +10558,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
@@ -10560,7 +10569,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B27" s="2">
         <v>3</v>
@@ -10629,7 +10638,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>19</v>
@@ -10641,7 +10650,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B37" s="3">
         <v>4</v>
@@ -10652,7 +10661,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B38" s="3">
         <v>4</v>
@@ -10663,7 +10672,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B39" s="3">
         <v>4</v>
@@ -10674,7 +10683,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B40" s="3">
         <v>5</v>
@@ -10685,7 +10694,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B41" s="3">
         <v>6</v>
@@ -10706,7 +10715,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>40</v>
@@ -10718,7 +10727,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="B46" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:3">
